--- a/output/details/2026-05-27/preprocessed_data.xlsx
+++ b/output/details/2026-05-27/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46169</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1160482197004931</v>
+        <v>-0.1216519603389047</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1415397755567105</v>
+        <v>-0.1407610149992362</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1413489964174949</v>
+        <v>-0.1404855834389126</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.119800778089442</v>
+        <v>-0.004050292293002068</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001697315075167276</v>
+        <v>0.001692977448265452</v>
       </c>
       <c r="G2" t="n">
-        <v>1.964710436147882</v>
+        <v>2.517108745767392</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4330523439688854</v>
+        <v>-0.2653707992684769</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
